--- a/docs/tutorials/files/xslope_rock_toppling.xlsx
+++ b/docs/tutorials/files/xslope_rock_toppling.xlsx
@@ -12161,7 +12161,7 @@
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
-        <v>44.0</v>
+        <v>26.0</v>
       </c>
       <c r="B13" s="3">
         <v>0.0</v>
@@ -12209,7 +12209,7 @@
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
-        <v>44.0</v>
+        <v>26.0</v>
       </c>
       <c r="B14" s="3">
         <v>-3.0</v>

--- a/docs/tutorials/files/xslope_rock_toppling.xlsx
+++ b/docs/tutorials/files/xslope_rock_toppling.xlsx
@@ -13223,20 +13223,10 @@
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
-        <v>17.46</v>
-      </c>
-      <c r="C3" s="3">
-        <v>24.0</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
-      </c>
-      <c r="E3" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
